--- a/document.xlsx
+++ b/document.xlsx
@@ -8,48 +8,13 @@
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Comparison"/>
-    <sheet name="second" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
-  <si>
-    <t>Benefit</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Entry</t>
-  </si>
-  <si>
-    <t>Plus</t>
-  </si>
-  <si>
-    <t>Primary Care</t>
-  </si>
-  <si>
-    <t>$15</t>
-  </si>
-  <si>
-    <t>Free</t>
-  </si>
-  <si>
-    <t>Vision</t>
-  </si>
-  <si>
-    <t>$0 copay</t>
-  </si>
-  <si>
-    <t>$10</t>
-  </si>
-  <si>
-    <t>This text should appear on sheet 2</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,59 +393,29 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
@@ -514,110 +449,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="25.005"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="2.005"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="20.005"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="2" width="2.005"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="20.005"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="2" width="2.005"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="20.005"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>